--- a/gap-analysis.xlsx
+++ b/gap-analysis.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2211" uniqueCount="909">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="914">
   <si>
     <t xml:space="preserve">WITYLOGIX — STARTUP ENGINEERING TEAM</t>
   </si>
@@ -303,7 +303,7 @@
     <t xml:space="preserve">Old Backend (lmd-oms-v3 + lmd-oms-nextjs-v3) → New Platform (witylogix-platform)</t>
   </si>
   <si>
-    <t xml:space="preserve">Last Updated: Sprint 2.5 (2026-03-06)</t>
+    <t xml:space="preserve">Last Updated: Sprint 2.6 (2026-03-07)</t>
   </si>
   <si>
     <t xml:space="preserve">Old System</t>
@@ -315,7 +315,7 @@
     <t xml:space="preserve">Gap</t>
   </si>
   <si>
-    <t xml:space="preserve">Total Files: 512 source files | 153,011 lines of code</t>
+    <t xml:space="preserve">Total Files: 555 source files | 168,753 lines of code</t>
   </si>
   <si>
     <t xml:space="preserve">38+</t>
@@ -618,327 +618,327 @@
     <t xml:space="preserve">Granular permission system missing</t>
   </si>
   <si>
+    <t xml:space="preserve">storeDetail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">store_details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">address, country, province, logo, favicon, social_links, business_hours, description, industry, defaultLanguage, supportEmail, returnPolicy, trackingPageConfig, widgetConfig, analyticsConfig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shop model is minimal vs old storeDetail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">storeSettings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">store_settings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shop.settings (JSON)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Structured settings: autoAssign, proofOfDelivery, signatureRequired, realTimeTracking, driverAppConfig, customerNotificationDefaults, inventorySync, fulfillmentRules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Old had explicit fields; new uses opaque JSON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">storeApiSettings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">store_api_settings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Old had dedicated model for API keys per provider (Google, Mapbox, Twilio, SendGrid, etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subsumed by Integration model but less explicit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP - Sanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">storeInfo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">store_infos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merged into Shop model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consolidated correctly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calenderRule / calenderProfile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calender_rules / calender_profiles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entire models: blackout_dates[], operating_hours{}, preparation_time, cutoff_rules, holiday_calendars, recurring_rules, capacity_by_day, special_event_overrides</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 2.5: calendar-engine.ts in shipping-profiles module</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VS - Vikram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deliveryRule / pickupRule / shippingRule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Various</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entire rule engines: distance-based, weight-based, zone-based, product-category, minimum-order, time-window, same-day/next-day rules, rate tables, conditional logic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 2.4 - DeliveryRule, PickupRule, CalendarProfile models added</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shippingProfile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shipping_profiles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ShippingProfile + ShippingRate + ShippingZoneRule + DeliveryCalendar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entire model: locations[], rates[], rules[], zones[], delivery_methods[], processing_times, conditions, product_groups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 2.5: 31-shipping-profiles-v2.prisma + full core module</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeliveryZone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boundary polygon (PostGIS), color, description, delivery_methods[], associated_locations[], max_distance, estimated_time_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PostGIS boundary is TODO; zone features limited</t>
+  </si>
+  <si>
+    <t xml:space="preserve">location / warehouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">locations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entire model: name, address, coordinates, type (warehouse/store/hub), inventory[], working_hours, pickup_rules, delivery_rules, associated_zones[], capacity, contact_info</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No location/warehouse model in new schema</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vehicle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vehicles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Driver (with vehicle fields)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Old had separate Vehicle model: make, model, year, color, insurance, registration, capacity_volume, capacity_weight, fuel_type, maintenance_schedule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New schema has vehicleType/vehiclePlate on Driver only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">notificationTemplate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">notification_templates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NotificationTemplate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entire model: channel, event_type, subject, body_template, variables[], isActive, language, version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notification template system missing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">notificationConfig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">notification_configs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NotificationLog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per-store notification preferences: enabled_channels{}, event_subscriptions{}, quiet_hours, frequency_limits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notification configuration missing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">whatsappTemplate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">whatsapp_templates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entire model: template_id, name, language, category, components[], status, provider_template_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WhatsApp Business template management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">campaign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">campaigns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entire model: name, type, audience_filter, template_ref, schedule, status, sent_count, open_rate, click_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaign/marketing module missing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">broadcastGroup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">broadcast_groups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entire model: name, type, member_filter, members[], metadata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Broadcast targeting missing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emailTemplate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">email_templates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entire model: name, subject, html_body, design_json (Unlayer), category, variables[]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email template editor/storage missing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paymentGateway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">payment_gateways</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PaymentMethod + PaymentTransaction + IdempotencyKey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entire model: provider, config, supported_methods[], fees, enabled, test_mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 2.5: 30-payments.prisma + payment processor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG - Rohan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">codGateway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cod_gateways</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CODCollection (in 30-payments.prisma)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entire model: enabled, verification_required, max_amount, collection_rules, reconciliation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 2.5: CODGateway class in payments module</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paymentTransaction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">payment_transactions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PaymentTransaction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entire model: order_ref, shipment_ref, amount, currency, method, status, provider_txn_id, refund_id, metadata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No transaction tracking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">products</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entire model: shopify_product_id, title, variants[], images[], tags[], product_type, vendor, weight, dimensions, inventory_quantity, metafields</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No product catalog in new schema</t>
+  </si>
+  <si>
+    <t xml:space="preserve">customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">customers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entire model: shopify_customer_id, name, email, phone, addresses[], orders_count, total_spent, tags[], notes, marketing_consent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No customer model in new schema</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entire model: shopify_collection_id, title, products[], type, sort_order, image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No collection model</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOT STARTED</t>
   </si>
   <si>
-    <t xml:space="preserve">storeDetail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">store_details</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">address, country, province, logo, favicon, social_links, business_hours, description, industry, defaultLanguage, supportEmail, returnPolicy, trackingPageConfig, widgetConfig, analyticsConfig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shop model is minimal vs old storeDetail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">storeSettings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">store_settings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shop.settings (JSON)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Structured settings: autoAssign, proofOfDelivery, signatureRequired, realTimeTracking, driverAppConfig, customerNotificationDefaults, inventorySync, fulfillmentRules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Old had explicit fields; new uses opaque JSON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">storeApiSettings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">store_api_settings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Old had dedicated model for API keys per provider (Google, Mapbox, Twilio, SendGrid, etc.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subsumed by Integration model but less explicit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SP - Sanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">storeInfo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">store_infos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merged into Shop model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consolidated correctly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">calenderRule / calenderProfile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">calender_rules / calender_profiles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entire models: blackout_dates[], operating_hours{}, preparation_time, cutoff_rules, holiday_calendars, recurring_rules, capacity_by_day, special_event_overrides</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint 2.5: calendar-engine.ts in shipping-profiles module</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VS - Vikram</t>
-  </si>
-  <si>
-    <t xml:space="preserve">deliveryRule / pickupRule / shippingRule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Various</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entire rule engines: distance-based, weight-based, zone-based, product-category, minimum-order, time-window, same-day/next-day rules, rate tables, conditional logic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint 2.4 - DeliveryRule, PickupRule, CalendarProfile models added</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shippingProfile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shipping_profiles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ShippingProfile + ShippingRate + ShippingZoneRule + DeliveryCalendar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entire model: locations[], rates[], rules[], zones[], delivery_methods[], processing_times, conditions, product_groups</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint 2.5: 31-shipping-profiles-v2.prisma + full core module</t>
-  </si>
-  <si>
-    <t xml:space="preserve">zone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">zones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DeliveryZone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boundary polygon (PostGIS), color, description, delivery_methods[], associated_locations[], max_distance, estimated_time_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PostGIS boundary is TODO; zone features limited</t>
-  </si>
-  <si>
-    <t xml:space="preserve">location / warehouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">locations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entire model: name, address, coordinates, type (warehouse/store/hub), inventory[], working_hours, pickup_rules, delivery_rules, associated_zones[], capacity, contact_info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No location/warehouse model in new schema</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vehicle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vehicles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Driver (with vehicle fields)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Old had separate Vehicle model: make, model, year, color, insurance, registration, capacity_volume, capacity_weight, fuel_type, maintenance_schedule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New schema has vehicleType/vehiclePlate on Driver only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">notificationTemplate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">notification_templates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NotificationTemplate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entire model: channel, event_type, subject, body_template, variables[], isActive, language, version</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notification template system missing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">notificationConfig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">notification_configs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NotificationLog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per-store notification preferences: enabled_channels{}, event_subscriptions{}, quiet_hours, frequency_limits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notification configuration missing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">whatsappTemplate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">whatsapp_templates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entire model: template_id, name, language, category, components[], status, provider_template_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WhatsApp Business template management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">campaigns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entire model: name, type, audience_filter, template_ref, schedule, status, sent_count, open_rate, click_rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campaign/marketing module missing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">broadcastGroup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">broadcast_groups</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entire model: name, type, member_filter, members[], metadata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Broadcast targeting missing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emailTemplate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">email_templates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entire model: name, subject, html_body, design_json (Unlayer), category, variables[]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email template editor/storage missing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">paymentGateway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">payment_gateways</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PaymentMethod + PaymentTransaction + IdempotencyKey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entire model: provider, config, supported_methods[], fees, enabled, test_mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint 2.5: 30-payments.prisma + payment processor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RG - Rohan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">codGateway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cod_gateways</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CODCollection (in 30-payments.prisma)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entire model: enabled, verification_required, max_amount, collection_rules, reconciliation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint 2.5: CODGateway class in payments module</t>
-  </si>
-  <si>
-    <t xml:space="preserve">paymentTransaction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">payment_transactions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PaymentTransaction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entire model: order_ref, shipment_ref, amount, currency, method, status, provider_txn_id, refund_id, metadata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No transaction tracking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">product</t>
-  </si>
-  <si>
-    <t xml:space="preserve">products</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entire model: shopify_product_id, title, variants[], images[], tags[], product_type, vendor, weight, dimensions, inventory_quantity, metafields</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No product catalog in new schema</t>
-  </si>
-  <si>
-    <t xml:space="preserve">customer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">customers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entire model: shopify_customer_id, name, email, phone, addresses[], orders_count, total_spent, tags[], notes, marketing_consent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No customer model in new schema</t>
-  </si>
-  <si>
-    <t xml:space="preserve">collection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">collections</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entire model: shopify_collection_id, title, products[], type, sort_order, image</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No collection model</t>
-  </si>
-  <si>
     <t xml:space="preserve">inventoryItem</t>
   </si>
   <si>
@@ -2649,7 +2649,7 @@
     <t xml:space="preserve">Gap Statistics Summary</t>
   </si>
   <si>
-    <t xml:space="preserve">SPRINT PROGRESS (as of Sprint 2.5)</t>
+    <t xml:space="preserve">SPRINT PROGRESS (as of Sprint 2.6)</t>
   </si>
   <si>
     <t xml:space="preserve">Metric</t>
@@ -2676,6 +2676,9 @@
     <t xml:space="preserve">Sprint 2.5</t>
   </si>
   <si>
+    <t xml:space="preserve">Sprint 2.6</t>
+  </si>
+  <si>
     <t xml:space="preserve">Source Files</t>
   </si>
   <si>
@@ -2734,6 +2737,18 @@
   </si>
   <si>
     <t xml:space="preserve">Migration framework + location management API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPRINT 2.6 DELIVERABLES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaign, messaging, audit, permissions API routes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 test suites (RBAC, audit, dispatcher, crypto, etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shopify campaigns, templates, audit log routes</t>
   </si>
   <si>
     <t xml:space="preserve">COMPLETION SUMMARY</t>
@@ -2771,7 +2786,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0%"/>
   </numFmts>
-  <fonts count="41">
+  <fonts count="42">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3062,6 +3077,13 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="10"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="12"/>
       <name val="Cambria"/>
       <family val="0"/>
@@ -3069,14 +3091,13 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFFACC15"/>
-      <name val="Arial"/>
+      <sz val="9"/>
+      <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3143,6 +3164,18 @@
         <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8D44D"/>
+        <bgColor rgb="FFFACC15"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFE0E0E0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
@@ -3187,7 +3220,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="106">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3544,11 +3577,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="39" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="40" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3580,11 +3613,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="38" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="27" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="40" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3592,7 +3629,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="40" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="41" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3601,6 +3638,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="41" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3820,11 +3861,11 @@
       <rgbColor rgb="FFA78BFA"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFE0E0E0"/>
       <rgbColor rgb="FF3B0D0D"/>
       <rgbColor rgb="FFF87171"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFE0E0E0"/>
+      <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF1A1A2E"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -3840,7 +3881,7 @@
       <rgbColor rgb="FF60A5FA"/>
       <rgbColor rgb="FFF472B6"/>
       <rgbColor rgb="FF818CF8"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFE8D44D"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF34D399"/>
       <rgbColor rgb="FF99CC00"/>
@@ -5185,7 +5226,7 @@
         <v>193</v>
       </c>
       <c r="H7" s="36" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="I7" s="41" t="s">
         <v>182</v>
@@ -5194,30 +5235,30 @@
         <v>17</v>
       </c>
       <c r="K7" s="42" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="26" t="s">
         <v>195</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="C8" s="26" t="s">
         <v>196</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>197</v>
       </c>
       <c r="D8" s="27" t="s">
         <v>156</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F8" s="27" t="s">
         <v>180</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H8" s="29" t="s">
         <v>160</v>
@@ -5234,25 +5275,25 @@
     </row>
     <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="C9" s="26" t="s">
         <v>201</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>202</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>156</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F9" s="27" t="s">
         <v>180</v>
       </c>
       <c r="G9" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H9" s="29" t="s">
         <v>160</v>
@@ -5269,31 +5310,31 @@
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="B10" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="C10" s="26" t="s">
         <v>206</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>207</v>
       </c>
       <c r="D10" s="27" t="s">
         <v>156</v>
       </c>
       <c r="E10" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="F10" s="43" t="s">
         <v>208</v>
       </c>
-      <c r="F10" s="43" t="s">
+      <c r="G10" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="G10" s="26" t="s">
+      <c r="H10" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="I10" s="44" t="s">
         <v>210</v>
-      </c>
-      <c r="H10" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="I10" s="44" t="s">
-        <v>211</v>
       </c>
       <c r="J10" s="31" t="s">
         <v>45</v>
@@ -5304,25 +5345,25 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="B11" s="11" t="s">
-        <v>213</v>
-      </c>
       <c r="C11" s="11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D11" s="45" t="s">
         <v>156</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>190</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H11" s="46" t="s">
         <v>160</v>
@@ -5339,10 +5380,10 @@
     </row>
     <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>216</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>217</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>190</v>
@@ -5351,19 +5392,19 @@
         <v>191</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F12" s="35" t="s">
         <v>158</v>
       </c>
       <c r="G12" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="H12" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="I12" s="49" t="s">
         <v>219</v>
-      </c>
-      <c r="H12" s="36" t="s">
-        <v>160</v>
-      </c>
-      <c r="I12" s="49" t="s">
-        <v>220</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>23</v>
@@ -5374,10 +5415,10 @@
     </row>
     <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>221</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>222</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>190</v>
@@ -5386,19 +5427,19 @@
         <v>156</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F13" s="51" t="s">
         <v>158</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H13" s="36" t="s">
         <v>160</v>
       </c>
       <c r="I13" s="52" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J13" s="12" t="s">
         <v>23</v>
@@ -5409,31 +5450,31 @@
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="C14" s="7" t="s">
         <v>226</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>227</v>
       </c>
       <c r="D14" s="34" t="s">
         <v>191</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F14" s="35" t="s">
         <v>158</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H14" s="36" t="s">
         <v>160</v>
       </c>
       <c r="I14" s="49" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J14" s="8" t="s">
         <v>23</v>
@@ -5444,31 +5485,31 @@
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="B15" s="26" t="s">
         <v>230</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="C15" s="26" t="s">
         <v>231</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>232</v>
       </c>
       <c r="D15" s="27" t="s">
         <v>156</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>180</v>
       </c>
       <c r="G15" s="26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H15" s="29" t="s">
         <v>160</v>
       </c>
       <c r="I15" s="53" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J15" s="31" t="s">
         <v>23</v>
@@ -5479,31 +5520,31 @@
     </row>
     <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="B16" s="26" t="s">
         <v>235</v>
       </c>
-      <c r="B16" s="26" t="s">
+      <c r="C16" s="26" t="s">
         <v>236</v>
-      </c>
-      <c r="C16" s="26" t="s">
-        <v>237</v>
       </c>
       <c r="D16" s="28" t="s">
         <v>156</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F16" s="28" t="s">
         <v>158</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H16" s="29" t="s">
         <v>160</v>
       </c>
       <c r="I16" s="53" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J16" s="31" t="s">
         <v>23</v>
@@ -5514,31 +5555,31 @@
     </row>
     <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="B17" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="C17" s="26" t="s">
         <v>241</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>242</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>156</v>
       </c>
       <c r="E17" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="F17" s="43" t="s">
+        <v>208</v>
+      </c>
+      <c r="G17" s="26" t="s">
         <v>243</v>
       </c>
-      <c r="F17" s="43" t="s">
-        <v>209</v>
-      </c>
-      <c r="G17" s="26" t="s">
-        <v>244</v>
-      </c>
       <c r="H17" s="29" t="s">
         <v>160</v>
       </c>
       <c r="I17" s="53" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J17" s="31" t="s">
         <v>23</v>
@@ -5549,31 +5590,31 @@
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="B18" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="C18" s="26" t="s">
         <v>246</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>247</v>
       </c>
       <c r="D18" s="28" t="s">
         <v>156</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F18" s="27" t="s">
         <v>180</v>
       </c>
       <c r="G18" s="26" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H18" s="29" t="s">
         <v>160</v>
       </c>
       <c r="I18" s="44" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J18" s="31" t="s">
         <v>45</v>
@@ -5584,31 +5625,31 @@
     </row>
     <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="B19" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="C19" s="26" t="s">
         <v>251</v>
-      </c>
-      <c r="C19" s="26" t="s">
-        <v>252</v>
       </c>
       <c r="D19" s="28" t="s">
         <v>156</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F19" s="27" t="s">
         <v>180</v>
       </c>
       <c r="G19" s="26" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H19" s="29" t="s">
         <v>160</v>
       </c>
       <c r="I19" s="44" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J19" s="31" t="s">
         <v>45</v>
@@ -5619,10 +5660,10 @@
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>255</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>256</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>190</v>
@@ -5631,33 +5672,33 @@
         <v>191</v>
       </c>
       <c r="E20" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="F20" s="54" t="s">
+        <v>208</v>
+      </c>
+      <c r="G20" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="F20" s="54" t="s">
-        <v>209</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>258</v>
-      </c>
       <c r="H20" s="36" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="I20" s="55" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J20" s="8" t="s">
         <v>45</v>
       </c>
       <c r="K20" s="38" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>259</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>260</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>190</v>
@@ -5666,33 +5707,33 @@
         <v>191</v>
       </c>
       <c r="E21" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="F21" s="56" t="s">
+        <v>208</v>
+      </c>
+      <c r="G21" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="F21" s="56" t="s">
-        <v>209</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>262</v>
-      </c>
       <c r="H21" s="36" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="I21" s="57" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J21" s="12" t="s">
         <v>45</v>
       </c>
       <c r="K21" s="42" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>263</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>264</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>190</v>
@@ -5701,33 +5742,33 @@
         <v>191</v>
       </c>
       <c r="E22" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="F22" s="54" t="s">
+        <v>208</v>
+      </c>
+      <c r="G22" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="F22" s="54" t="s">
-        <v>209</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>266</v>
-      </c>
       <c r="H22" s="36" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="I22" s="55" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J22" s="8" t="s">
         <v>45</v>
       </c>
       <c r="K22" s="38" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>267</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>268</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>190</v>
@@ -5736,54 +5777,54 @@
         <v>191</v>
       </c>
       <c r="E23" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="F23" s="56" t="s">
+        <v>208</v>
+      </c>
+      <c r="G23" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="F23" s="56" t="s">
-        <v>209</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>270</v>
-      </c>
       <c r="H23" s="36" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="I23" s="57" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J23" s="12" t="s">
         <v>45</v>
       </c>
       <c r="K23" s="42" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="C24" s="7" t="s">
         <v>272</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>273</v>
       </c>
       <c r="D24" s="34" t="s">
         <v>191</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F24" s="58" t="s">
         <v>180</v>
       </c>
       <c r="G24" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="H24" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="I24" s="59" t="s">
         <v>275</v>
-      </c>
-      <c r="H24" s="36" t="s">
-        <v>160</v>
-      </c>
-      <c r="I24" s="59" t="s">
-        <v>276</v>
       </c>
       <c r="J24" s="8" t="s">
         <v>45</v>
@@ -5794,31 +5835,31 @@
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="C25" s="11" t="s">
         <v>278</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>279</v>
       </c>
       <c r="D25" s="34" t="s">
         <v>191</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F25" s="40" t="s">
         <v>180</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H25" s="36" t="s">
         <v>160</v>
       </c>
       <c r="I25" s="60" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J25" s="12" t="s">
         <v>45</v>
@@ -5829,31 +5870,31 @@
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="26" t="s">
+        <v>281</v>
+      </c>
+      <c r="B26" s="26" t="s">
         <v>282</v>
       </c>
-      <c r="B26" s="26" t="s">
+      <c r="C26" s="26" t="s">
         <v>283</v>
-      </c>
-      <c r="C26" s="26" t="s">
-        <v>284</v>
       </c>
       <c r="D26" s="28" t="s">
         <v>156</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F26" s="27" t="s">
         <v>180</v>
       </c>
       <c r="G26" s="26" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H26" s="29" t="s">
         <v>160</v>
       </c>
       <c r="I26" s="61" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J26" s="31" t="s">
         <v>45</v>
@@ -5864,25 +5905,25 @@
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="B27" s="26" t="s">
         <v>287</v>
       </c>
-      <c r="B27" s="26" t="s">
+      <c r="C27" s="26" t="s">
         <v>288</v>
-      </c>
-      <c r="C27" s="26" t="s">
-        <v>289</v>
       </c>
       <c r="D27" s="28" t="s">
         <v>156</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F27" s="27" t="s">
         <v>180</v>
       </c>
       <c r="G27" s="26" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H27" s="29" t="s">
         <v>160</v>
@@ -5899,25 +5940,25 @@
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="B28" s="26" t="s">
         <v>292</v>
       </c>
-      <c r="B28" s="26" t="s">
+      <c r="C28" s="26" t="s">
         <v>293</v>
-      </c>
-      <c r="C28" s="26" t="s">
-        <v>294</v>
       </c>
       <c r="D28" s="28" t="s">
         <v>156</v>
       </c>
       <c r="E28" s="26" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F28" s="27" t="s">
         <v>180</v>
       </c>
       <c r="G28" s="26" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H28" s="29" t="s">
         <v>160</v>
@@ -5934,10 +5975,10 @@
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>297</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>298</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>190</v>
@@ -5946,13 +5987,13 @@
         <v>191</v>
       </c>
       <c r="E29" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="F29" s="56" t="s">
+        <v>208</v>
+      </c>
+      <c r="G29" s="11" t="s">
         <v>299</v>
-      </c>
-      <c r="F29" s="56" t="s">
-        <v>209</v>
-      </c>
-      <c r="G29" s="11" t="s">
-        <v>300</v>
       </c>
       <c r="H29" s="36" t="s">
         <v>174</v>
@@ -5964,7 +6005,7 @@
         <v>23</v>
       </c>
       <c r="K29" s="42" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6104,7 +6145,7 @@
         <v>34</v>
       </c>
       <c r="K33" s="42" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6124,7 +6165,7 @@
         <v>322</v>
       </c>
       <c r="F34" s="54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>323</v>
@@ -6159,7 +6200,7 @@
         <v>326</v>
       </c>
       <c r="F35" s="56" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G35" s="11" t="s">
         <v>327</v>
@@ -6168,13 +6209,13 @@
         <v>174</v>
       </c>
       <c r="I35" s="60" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J35" s="12" t="s">
         <v>45</v>
       </c>
       <c r="K35" s="42" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6203,13 +6244,13 @@
         <v>174</v>
       </c>
       <c r="I36" s="59" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J36" s="8" t="s">
         <v>45</v>
       </c>
       <c r="K36" s="38" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6238,13 +6279,13 @@
         <v>174</v>
       </c>
       <c r="I37" s="60" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J37" s="12" t="s">
         <v>45</v>
       </c>
       <c r="K37" s="42" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6273,7 +6314,7 @@
         <v>174</v>
       </c>
       <c r="I38" s="59" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J38" s="8" t="s">
         <v>45</v>
@@ -6308,7 +6349,7 @@
         <v>174</v>
       </c>
       <c r="I39" s="60" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J39" s="12" t="s">
         <v>45</v>
@@ -6343,7 +6384,7 @@
         <v>174</v>
       </c>
       <c r="I40" s="59" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J40" s="8" t="s">
         <v>45</v>
@@ -6716,7 +6757,7 @@
         <v>34</v>
       </c>
       <c r="J10" s="38" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7062,7 +7103,7 @@
         <v>160</v>
       </c>
       <c r="H21" s="44" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I21" s="31" t="s">
         <v>45</v>
@@ -7094,7 +7135,7 @@
         <v>160</v>
       </c>
       <c r="H22" s="44" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I22" s="31" t="s">
         <v>45</v>
@@ -7184,7 +7225,7 @@
         <v>447</v>
       </c>
       <c r="F25" s="43" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G25" s="29" t="s">
         <v>160</v>
@@ -7286,7 +7327,7 @@
         <v>160</v>
       </c>
       <c r="H28" s="61" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I28" s="31" t="s">
         <v>45</v>
@@ -7312,13 +7353,13 @@
         <v>463</v>
       </c>
       <c r="F29" s="43" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G29" s="29" t="s">
         <v>160</v>
       </c>
       <c r="H29" s="61" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I29" s="31" t="s">
         <v>45</v>
@@ -7344,13 +7385,13 @@
         <v>466</v>
       </c>
       <c r="F30" s="54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G30" s="36" t="s">
         <v>160</v>
       </c>
       <c r="H30" s="59" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I30" s="8" t="s">
         <v>45</v>
@@ -7376,7 +7417,7 @@
         <v>469</v>
       </c>
       <c r="F31" s="56" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G31" s="36" t="s">
         <v>174</v>
@@ -7388,7 +7429,7 @@
         <v>34</v>
       </c>
       <c r="J31" s="42" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7408,7 +7449,7 @@
         <v>472</v>
       </c>
       <c r="F32" s="54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G32" s="36" t="s">
         <v>160</v>
@@ -7478,7 +7519,7 @@
         <v>160</v>
       </c>
       <c r="H34" s="59" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I34" s="8" t="s">
         <v>45</v>
@@ -7504,7 +7545,7 @@
         <v>482</v>
       </c>
       <c r="F35" s="69" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G35" s="69" t="s">
         <v>160</v>
@@ -7536,7 +7577,7 @@
         <v>485</v>
       </c>
       <c r="F36" s="69" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G36" s="69" t="s">
         <v>160</v>
@@ -7632,7 +7673,7 @@
         <v>494</v>
       </c>
       <c r="F39" s="69" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G39" s="69" t="s">
         <v>160</v>
@@ -7664,7 +7705,7 @@
         <v>498</v>
       </c>
       <c r="F40" s="69" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G40" s="69" t="s">
         <v>160</v>
@@ -7877,7 +7918,7 @@
         <v>160</v>
       </c>
       <c r="H5" s="52" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I5" s="12" t="s">
         <v>23</v>
@@ -7909,7 +7950,7 @@
         <v>160</v>
       </c>
       <c r="H6" s="53" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I6" s="31" t="s">
         <v>23</v>
@@ -7941,7 +7982,7 @@
         <v>160</v>
       </c>
       <c r="H7" s="52" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I7" s="12" t="s">
         <v>23</v>
@@ -7973,7 +8014,7 @@
         <v>160</v>
       </c>
       <c r="H8" s="49" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I8" s="8" t="s">
         <v>23</v>
@@ -8005,7 +8046,7 @@
         <v>160</v>
       </c>
       <c r="H9" s="52" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I9" s="12" t="s">
         <v>23</v>
@@ -8037,7 +8078,7 @@
         <v>160</v>
       </c>
       <c r="H10" s="53" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I10" s="31" t="s">
         <v>23</v>
@@ -8069,7 +8110,7 @@
         <v>160</v>
       </c>
       <c r="H11" s="57" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I11" s="12" t="s">
         <v>45</v>
@@ -8101,7 +8142,7 @@
         <v>160</v>
       </c>
       <c r="H12" s="55" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I12" s="8" t="s">
         <v>45</v>
@@ -8197,7 +8238,7 @@
         <v>160</v>
       </c>
       <c r="H15" s="57" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I15" s="12" t="s">
         <v>45</v>
@@ -8229,7 +8270,7 @@
         <v>160</v>
       </c>
       <c r="H16" s="59" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I16" s="8" t="s">
         <v>45</v>
@@ -8261,7 +8302,7 @@
         <v>160</v>
       </c>
       <c r="H17" s="60" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I17" s="12" t="s">
         <v>45</v>
@@ -8293,7 +8334,7 @@
         <v>160</v>
       </c>
       <c r="H18" s="55" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I18" s="8" t="s">
         <v>45</v>
@@ -8325,7 +8366,7 @@
         <v>160</v>
       </c>
       <c r="H19" s="60" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I19" s="12" t="s">
         <v>45</v>
@@ -8357,7 +8398,7 @@
         <v>160</v>
       </c>
       <c r="H20" s="61" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I20" s="31" t="s">
         <v>45</v>
@@ -8450,7 +8491,7 @@
         <v>180</v>
       </c>
       <c r="G23" s="36" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="H23" s="41" t="s">
         <v>182</v>
@@ -8459,7 +8500,7 @@
         <v>17</v>
       </c>
       <c r="J23" s="42" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8511,19 +8552,19 @@
         <v>588</v>
       </c>
       <c r="F25" s="56" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G25" s="36" t="s">
         <v>174</v>
       </c>
       <c r="H25" s="60" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I25" s="12" t="s">
         <v>45</v>
       </c>
       <c r="J25" s="42" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8645,13 +8686,13 @@
         <v>174</v>
       </c>
       <c r="H29" s="57" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I29" s="12" t="s">
         <v>45</v>
       </c>
       <c r="J29" s="42" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8677,13 +8718,13 @@
         <v>174</v>
       </c>
       <c r="H30" s="55" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I30" s="8" t="s">
         <v>45</v>
       </c>
       <c r="J30" s="38" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8703,19 +8744,19 @@
         <v>609</v>
       </c>
       <c r="F31" s="56" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G31" s="36" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="H31" s="60" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I31" s="12" t="s">
         <v>45</v>
       </c>
       <c r="J31" s="42" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8831,7 +8872,7 @@
         <v>622</v>
       </c>
       <c r="F35" s="69" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G35" s="69" t="s">
         <v>160</v>
@@ -8927,7 +8968,7 @@
         <v>622</v>
       </c>
       <c r="F38" s="69" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G38" s="69" t="s">
         <v>160</v>
@@ -8959,7 +9000,7 @@
         <v>622</v>
       </c>
       <c r="F39" s="69" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G39" s="69" t="s">
         <v>160</v>
@@ -9023,7 +9064,7 @@
         <v>622</v>
       </c>
       <c r="F41" s="69" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G41" s="69" t="s">
         <v>160</v>
@@ -9055,7 +9096,7 @@
         <v>622</v>
       </c>
       <c r="F42" s="69" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G42" s="69" t="s">
         <v>160</v>
@@ -9087,7 +9128,7 @@
         <v>622</v>
       </c>
       <c r="F43" s="69" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G43" s="69" t="s">
         <v>160</v>
@@ -9119,7 +9160,7 @@
         <v>622</v>
       </c>
       <c r="F44" s="69" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G44" s="69" t="s">
         <v>160</v>
@@ -9247,7 +9288,7 @@
         <v>622</v>
       </c>
       <c r="F48" s="69" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G48" s="69" t="s">
         <v>160</v>
@@ -9279,7 +9320,7 @@
         <v>622</v>
       </c>
       <c r="F49" s="69" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G49" s="69" t="s">
         <v>160</v>
@@ -9311,7 +9352,7 @@
         <v>622</v>
       </c>
       <c r="F50" s="69" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G50" s="69" t="s">
         <v>160</v>
@@ -9626,7 +9667,7 @@
         <v>55</v>
       </c>
       <c r="J7" s="42" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9684,7 +9725,7 @@
         <v>160</v>
       </c>
       <c r="H9" s="44" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I9" s="31" t="s">
         <v>45</v>
@@ -9716,7 +9757,7 @@
         <v>160</v>
       </c>
       <c r="H10" s="44" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I10" s="31" t="s">
         <v>45</v>
@@ -9745,16 +9786,16 @@
         <v>180</v>
       </c>
       <c r="G11" s="36" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="H11" s="57" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I11" s="12" t="s">
         <v>45</v>
       </c>
       <c r="J11" s="42" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9777,16 +9818,16 @@
         <v>180</v>
       </c>
       <c r="G12" s="36" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="H12" s="55" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I12" s="8" t="s">
         <v>45</v>
       </c>
       <c r="J12" s="38" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9870,7 +9911,7 @@
         <v>707</v>
       </c>
       <c r="F15" s="56" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G15" s="36" t="s">
         <v>160</v>
@@ -10030,10 +10071,10 @@
         <v>724</v>
       </c>
       <c r="F20" s="54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G20" s="36" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="H20" s="70" t="s">
         <v>600</v>
@@ -10042,7 +10083,7 @@
         <v>55</v>
       </c>
       <c r="J20" s="38" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10065,7 +10106,7 @@
         <v>180</v>
       </c>
       <c r="G21" s="36" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="H21" s="41" t="s">
         <v>182</v>
@@ -10074,7 +10115,7 @@
         <v>17</v>
       </c>
       <c r="J21" s="42" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10094,7 +10135,7 @@
         <v>731</v>
       </c>
       <c r="F22" s="69" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G22" s="69" t="s">
         <v>160</v>
@@ -10158,7 +10199,7 @@
         <v>738</v>
       </c>
       <c r="F24" s="69" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G24" s="69" t="s">
         <v>160</v>
@@ -10387,7 +10428,7 @@
         <v>160</v>
       </c>
       <c r="I5" s="53" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J5" s="31" t="s">
         <v>23</v>
@@ -10422,7 +10463,7 @@
         <v>160</v>
       </c>
       <c r="I6" s="53" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J6" s="31" t="s">
         <v>23</v>
@@ -10457,7 +10498,7 @@
         <v>160</v>
       </c>
       <c r="I7" s="53" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J7" s="31" t="s">
         <v>23</v>
@@ -10562,7 +10603,7 @@
         <v>160</v>
       </c>
       <c r="I10" s="53" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J10" s="31" t="s">
         <v>23</v>
@@ -10702,7 +10743,7 @@
         <v>160</v>
       </c>
       <c r="I14" s="44" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J14" s="31" t="s">
         <v>45</v>
@@ -10737,7 +10778,7 @@
         <v>160</v>
       </c>
       <c r="I15" s="44" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J15" s="31" t="s">
         <v>45</v>
@@ -10772,7 +10813,7 @@
         <v>160</v>
       </c>
       <c r="I16" s="55" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J16" s="8" t="s">
         <v>45</v>
@@ -10807,7 +10848,7 @@
         <v>160</v>
       </c>
       <c r="I17" s="44" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J17" s="31" t="s">
         <v>45</v>
@@ -10842,7 +10883,7 @@
         <v>160</v>
       </c>
       <c r="I18" s="44" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J18" s="31" t="s">
         <v>45</v>
@@ -10947,7 +10988,7 @@
         <v>160</v>
       </c>
       <c r="I21" s="79" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J21" s="80" t="s">
         <v>45</v>
@@ -10982,7 +11023,7 @@
         <v>160</v>
       </c>
       <c r="I22" s="53" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J22" s="31" t="s">
         <v>23</v>
@@ -11087,7 +11128,7 @@
         <v>160</v>
       </c>
       <c r="I25" s="61" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J25" s="31" t="s">
         <v>45</v>
@@ -11122,7 +11163,7 @@
         <v>160</v>
       </c>
       <c r="I26" s="61" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J26" s="31" t="s">
         <v>45</v>
@@ -11262,7 +11303,7 @@
         <v>160</v>
       </c>
       <c r="I30" s="59" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J30" s="8" t="s">
         <v>45</v>
@@ -11297,7 +11338,7 @@
         <v>160</v>
       </c>
       <c r="I31" s="57" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J31" s="12" t="s">
         <v>45</v>
@@ -11367,13 +11408,13 @@
         <v>174</v>
       </c>
       <c r="I33" s="60" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J33" s="12" t="s">
         <v>45</v>
       </c>
       <c r="K33" s="42" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11514,7 +11555,7 @@
     <tabColor rgb="FFFB923C"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
@@ -11536,7 +11577,9 @@
       <c r="E3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11"/>
+      <c r="A4" s="11" t="s">
+        <v>89</v>
+      </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
@@ -11561,16 +11604,19 @@
       <c r="F5" s="88" t="s">
         <v>877</v>
       </c>
-      <c r="G5" s="89" t="s">
+      <c r="G5" s="88" t="s">
         <v>878</v>
       </c>
-      <c r="H5" s="89" t="s">
+      <c r="H5" s="88" t="s">
         <v>879</v>
+      </c>
+      <c r="I5" s="89" t="s">
+        <v>880</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>184</v>
@@ -11587,16 +11633,19 @@
       <c r="F6" s="1" t="n">
         <v>429</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="1" t="n">
         <v>461</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="1" t="n">
         <v>512</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>555</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B7" s="7" t="n">
         <v>22541</v>
@@ -11613,16 +11662,19 @@
       <c r="F7" s="1" t="n">
         <v>113346</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7" s="1" t="n">
         <v>130966</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="1" t="n">
         <v>153011</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>168753</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B8" s="10" t="n">
         <v>10</v>
@@ -11639,10 +11691,13 @@
       <c r="F8" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="I8" s="1" t="n">
         <v>50</v>
       </c>
     </row>
@@ -11665,16 +11720,19 @@
       <c r="F9" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9" s="1" t="n">
         <v>42</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>18</v>
@@ -11691,16 +11749,19 @@
       <c r="F10" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="H10" s="1" t="n">
         <v>26</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>4</v>
@@ -11717,16 +11778,19 @@
       <c r="F11" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="H11" s="0" t="n">
+      <c r="H11" s="1" t="n">
         <v>38</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>0</v>
@@ -11743,11 +11807,14 @@
       <c r="F12" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="G12" s="0" t="n">
+      <c r="G12" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="H12" s="0" t="n">
+      <c r="H12" s="1" t="n">
         <v>37</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11760,7 +11827,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="90" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B14" s="87"/>
       <c r="C14" s="87"/>
@@ -11778,16 +11845,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="87" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B16" s="87" t="s">
         <v>746</v>
       </c>
       <c r="C16" s="87" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="D16" s="87" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="E16" s="87" t="s">
         <v>146</v>
@@ -11799,7 +11866,7 @@
         <v>182</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C17" s="10" t="n">
         <v>7</v>
@@ -11817,7 +11884,7 @@
         <v>363</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>3</v>
@@ -11834,7 +11901,7 @@
         <v>319</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>5</v>
@@ -11848,10 +11915,10 @@
     </row>
     <row r="20" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>10</v>
@@ -11866,10 +11933,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="94" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>6</v>
@@ -11884,10 +11951,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="62" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C22" s="12" t="n">
         <v>6</v>
@@ -11905,7 +11972,7 @@
         <v>161</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C23" s="8" t="n">
         <v>6</v>
@@ -11920,10 +11987,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="63" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C24" s="12" t="n">
         <v>8</v>
@@ -11941,7 +12008,7 @@
         <v>600</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C25" s="8" t="n">
         <v>5</v>
@@ -11963,173 +12030,235 @@
       <c r="F26" s="41"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="59" t="s">
-        <v>900</v>
+      <c r="A27" s="98" t="s">
+        <v>901</v>
       </c>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
       <c r="D27" s="95"/>
-      <c r="E27" s="98"/>
+      <c r="E27" s="99"/>
       <c r="F27" s="94"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="99" t="s">
-        <v>900</v>
-      </c>
-      <c r="B28" s="100"/>
-      <c r="C28" s="100"/>
-      <c r="D28" s="100"/>
-      <c r="E28" s="100"/>
-      <c r="F28" s="100"/>
+      <c r="A28" s="100"/>
+      <c r="B28" s="101"/>
+      <c r="C28" s="101"/>
+      <c r="D28" s="101"/>
+      <c r="E28" s="101"/>
+      <c r="F28" s="101"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="101" t="s">
+      <c r="A29" s="102"/>
+      <c r="B29" s="102"/>
+      <c r="C29" s="102"/>
+      <c r="D29" s="102"/>
+      <c r="E29" s="102"/>
+      <c r="F29" s="94"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="88"/>
+      <c r="B30" s="88"/>
+      <c r="C30" s="88"/>
+      <c r="D30" s="88"/>
+      <c r="E30" s="88"/>
+      <c r="F30" s="103"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F31" s="104"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F32" s="104"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F33" s="104"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F34" s="104"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>2469</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="D37" s="1" t="n">
+        <v>4725</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>1628</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="88" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="105" t="s">
         <v>743</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B42" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C42" s="105" t="s">
         <v>150</v>
       </c>
-      <c r="D29" s="95" t="s">
-        <v>901</v>
-      </c>
-      <c r="E29" s="98" t="s">
-        <v>902</v>
-      </c>
-      <c r="F29" s="94" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="88" t="s">
-        <v>743</v>
-      </c>
-      <c r="B30" s="88" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" s="88" t="s">
-        <v>150</v>
-      </c>
-      <c r="D30" s="88" t="s">
-        <v>901</v>
-      </c>
-      <c r="E30" s="88" t="s">
-        <v>902</v>
-      </c>
-      <c r="F30" s="102" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>904</v>
-      </c>
-      <c r="B31" s="1" t="n">
+      <c r="D42" s="105" t="s">
+        <v>906</v>
+      </c>
+      <c r="E42" s="105" t="s">
+        <v>907</v>
+      </c>
+      <c r="F42" s="105" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="B43" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C43" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="D43" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" s="1" t="n">
+        <f aca="false">B43-C43-D43</f>
+        <v>10</v>
+      </c>
+      <c r="F43" s="104" t="n">
+        <f aca="false">C43/B43</f>
+        <v>0.666666666666667</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="1" t="n">
+        <f aca="false">B44-C44-D44</f>
+        <v>6</v>
+      </c>
+      <c r="F44" s="104" t="n">
+        <f aca="false">C44/B44</f>
+        <v>0.823529411764706</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="C45" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <f aca="false">B45-C45-D45</f>
+        <v>0</v>
+      </c>
+      <c r="F45" s="104" t="n">
+        <f aca="false">C45/B45</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="B46" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="D31" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <f aca="false">B31-C31-D31</f>
+      <c r="C46" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="F31" s="103" t="n">
-        <f aca="false">C31/B31</f>
-        <v>0.538461538461538</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
-        <v>905</v>
-      </c>
-      <c r="B32" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="C32" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="D32" s="1" t="n">
+      <c r="D46" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E32" s="1" t="n">
-        <f aca="false">B32-C32-D32</f>
+      <c r="E46" s="1" t="n">
+        <f aca="false">B46-C46-D46</f>
         <v>6</v>
       </c>
-      <c r="F32" s="103" t="n">
-        <f aca="false">C32/B32</f>
-        <v>0.823529411764706</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
-        <v>906</v>
-      </c>
-      <c r="B33" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="C33" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <f aca="false">B33-C33-D33</f>
+      <c r="F46" s="104" t="n">
+        <f aca="false">C46/B46</f>
+        <v>0.714285714285714</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="D47" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="F33" s="103" t="n">
-        <f aca="false">C33/B33</f>
-        <v>0.941176470588235</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
-        <v>907</v>
-      </c>
-      <c r="B34" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <f aca="false">B34-C34-D34</f>
-        <v>9</v>
-      </c>
-      <c r="F34" s="103" t="n">
-        <f aca="false">C34/B34</f>
-        <v>0.523809523809524</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <f aca="false">B35-C35-D35</f>
-        <v>9</v>
-      </c>
-      <c r="F35" s="1" t="n">
-        <f aca="false">C35/B35</f>
-        <v>0.657142857142857</v>
+      <c r="E47" s="1" t="n">
+        <f aca="false">B47-C47-D47</f>
+        <v>8</v>
+      </c>
+      <c r="F47" s="104" t="n">
+        <f aca="false">C47/B47</f>
+        <v>0.714285714285714</v>
       </c>
     </row>
   </sheetData>

--- a/gap-analysis.xlsx
+++ b/gap-analysis.xlsx
@@ -32,7 +32,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="47">
+  <fonts count="48">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -363,6 +363,11 @@
     <font>
       <color rgb="00228B22"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00E67E22"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="16">
     <fill>
@@ -482,7 +487,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="220">
+  <cellXfs count="221">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1133,6 +1138,7 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="45" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1599,6 +1605,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26.25" customHeight="1" s="107">
       <c r="A4" s="110" t="inlineStr">
         <is>
@@ -2201,6 +2208,7 @@
         <v/>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="17.25" customHeight="1" s="107">
       <c r="A16" s="130" t="inlineStr">
         <is>
@@ -2403,6 +2411,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="107">
       <c r="A4" s="110" t="inlineStr">
         <is>
@@ -2729,7 +2738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="28" customWidth="1" style="106" min="1" max="1"/>
@@ -2933,7 +2942,7 @@
       </c>
       <c r="D4" s="140" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>EXISTS</t>
         </is>
       </c>
       <c r="E4" s="113" t="inlineStr">
@@ -2948,12 +2957,12 @@
       </c>
       <c r="G4" s="113" t="inlineStr">
         <is>
-          <t>Needed for per-item shipment tracking</t>
+          <t>Sprint 2.7 - 36-shipment-items.prisma</t>
         </is>
       </c>
       <c r="H4" s="142" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="I4" s="143" t="inlineStr">
@@ -4358,7 +4367,7 @@
       </c>
       <c r="D29" s="140" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>EXISTS</t>
         </is>
       </c>
       <c r="E29" s="117" t="inlineStr">
@@ -4373,12 +4382,12 @@
       </c>
       <c r="G29" s="117" t="inlineStr">
         <is>
-          <t>No collection model</t>
+          <t>Sprint 2.7</t>
         </is>
       </c>
       <c r="H29" s="142" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="I29" s="168" t="inlineStr">
@@ -4586,7 +4595,7 @@
       </c>
       <c r="D33" s="140" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>EXISTS</t>
         </is>
       </c>
       <c r="E33" s="117" t="inlineStr">
@@ -4601,12 +4610,12 @@
       </c>
       <c r="G33" s="117" t="inlineStr">
         <is>
-          <t>Saved table views/filters per user</t>
+          <t>Sprint 2.7</t>
         </is>
       </c>
       <c r="H33" s="142" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="I33" s="169" t="inlineStr">
@@ -4700,7 +4709,7 @@
       </c>
       <c r="D35" s="140" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>EXISTS</t>
         </is>
       </c>
       <c r="E35" s="117" t="inlineStr">
@@ -4715,12 +4724,12 @@
       </c>
       <c r="G35" s="117" t="inlineStr">
         <is>
-          <t>Checkout widget configuration missing</t>
+          <t>Sprint 2.7</t>
         </is>
       </c>
       <c r="H35" s="142" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="I35" s="166" t="inlineStr">
@@ -4757,7 +4766,7 @@
       </c>
       <c r="D36" s="140" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>EXISTS</t>
         </is>
       </c>
       <c r="E36" s="113" t="inlineStr">
@@ -4772,12 +4781,12 @@
       </c>
       <c r="G36" s="113" t="inlineStr">
         <is>
-          <t>Support ticket system missing</t>
+          <t>Sprint 2.7</t>
         </is>
       </c>
       <c r="H36" s="142" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="I36" s="165" t="inlineStr">
@@ -4814,7 +4823,7 @@
       </c>
       <c r="D37" s="140" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>EXISTS</t>
         </is>
       </c>
       <c r="E37" s="117" t="inlineStr">
@@ -4829,12 +4838,12 @@
       </c>
       <c r="G37" s="117" t="inlineStr">
         <is>
-          <t>Feature request tracking missing</t>
+          <t>Sprint 2.7</t>
         </is>
       </c>
       <c r="H37" s="142" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="I37" s="166" t="inlineStr">
@@ -4871,7 +4880,7 @@
       </c>
       <c r="D38" s="140" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>EXISTS</t>
         </is>
       </c>
       <c r="E38" s="113" t="inlineStr">
@@ -4886,12 +4895,12 @@
       </c>
       <c r="G38" s="113" t="inlineStr">
         <is>
-          <t>Usage metering / quota enforcement missing</t>
+          <t>Sprint 2.7</t>
         </is>
       </c>
       <c r="H38" s="142" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="I38" s="165" t="inlineStr">
@@ -4928,7 +4937,7 @@
       </c>
       <c r="D39" s="140" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>EXISTS</t>
         </is>
       </c>
       <c r="E39" s="117" t="inlineStr">
@@ -4943,12 +4952,12 @@
       </c>
       <c r="G39" s="117" t="inlineStr">
         <is>
-          <t>Billing plan catalog missing</t>
+          <t>Sprint 2.7</t>
         </is>
       </c>
       <c r="H39" s="142" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="I39" s="166" t="inlineStr">
@@ -4985,7 +4994,7 @@
       </c>
       <c r="D40" s="140" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>EXISTS</t>
         </is>
       </c>
       <c r="E40" s="113" t="inlineStr">
@@ -5000,27 +5009,203 @@
       </c>
       <c r="G40" s="113" t="inlineStr">
         <is>
-          <t>Subscription management missing</t>
+          <t>Sprint 2.7</t>
         </is>
       </c>
       <c r="H40" s="142" t="inlineStr">
         <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="I40" s="165" t="inlineStr">
+        <is>
+          <t>RG - Rohan</t>
+        </is>
+      </c>
+      <c r="J40" s="114" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
+      <c r="K40" s="144" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="220" t="inlineStr">
+        <is>
+          <t>SPRINT 2.8 PLANNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="106" t="inlineStr">
+        <is>
+          <t>authProvider</t>
+        </is>
+      </c>
+      <c r="B43" s="106" t="inlineStr">
+        <is>
+          <t>auth_providers</t>
+        </is>
+      </c>
+      <c r="C43" s="106" t="inlineStr">
+        <is>
+          <t>AuthProvider</t>
+        </is>
+      </c>
+      <c r="D43" s="106" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="E43" s="106" t="inlineStr">
+        <is>
+          <t>provider, type (auth0/clerk/cognito/firebase), config, enabled, tenant_scope</t>
+        </is>
+      </c>
+      <c r="F43" s="106" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G43" s="106" t="inlineStr">
+        <is>
+          <t>Sprint 2.8 - Auth provider registry</t>
+        </is>
+      </c>
+      <c r="H43" s="106" t="inlineStr">
+        <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="I40" s="165" t="inlineStr">
-        <is>
-          <t>RG - Rohan</t>
-        </is>
-      </c>
-      <c r="J40" s="114" t="inlineStr">
-        <is>
-          <t>Integrations</t>
-        </is>
-      </c>
-      <c r="K40" s="144" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+    </row>
+    <row r="44">
+      <c r="A44" s="106" t="inlineStr">
+        <is>
+          <t>authSession</t>
+        </is>
+      </c>
+      <c r="B44" s="106" t="inlineStr">
+        <is>
+          <t>auth_sessions</t>
+        </is>
+      </c>
+      <c r="C44" s="106" t="inlineStr">
+        <is>
+          <t>AuthSession</t>
+        </is>
+      </c>
+      <c r="D44" s="106" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="E44" s="106" t="inlineStr">
+        <is>
+          <t>userId, provider, externalId, accessToken, refreshToken, expiresAt, metadata</t>
+        </is>
+      </c>
+      <c r="F44" s="106" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G44" s="106" t="inlineStr">
+        <is>
+          <t>Sprint 2.8 - External auth sessions</t>
+        </is>
+      </c>
+      <c r="H44" s="106" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="106" t="inlineStr">
+        <is>
+          <t>platformAdmin</t>
+        </is>
+      </c>
+      <c r="B45" s="106" t="inlineStr">
+        <is>
+          <t>platform_admins</t>
+        </is>
+      </c>
+      <c r="C45" s="106" t="inlineStr">
+        <is>
+          <t>PlatformAdmin</t>
+        </is>
+      </c>
+      <c r="D45" s="106" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="E45" s="106" t="inlineStr">
+        <is>
+          <t>email, role (super/admin/support), permissions, lastLogin, mfaEnabled</t>
+        </is>
+      </c>
+      <c r="F45" s="106" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G45" s="106" t="inlineStr">
+        <is>
+          <t>Sprint 2.8 - Platform admin panel</t>
+        </is>
+      </c>
+      <c r="H45" s="106" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="106" t="inlineStr">
+        <is>
+          <t>posConfig</t>
+        </is>
+      </c>
+      <c r="B46" s="106" t="inlineStr">
+        <is>
+          <t>pos_configs</t>
+        </is>
+      </c>
+      <c r="C46" s="106" t="inlineStr">
+        <is>
+          <t>POSConfig</t>
+        </is>
+      </c>
+      <c r="D46" s="106" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="E46" s="106" t="inlineStr">
+        <is>
+          <t>shopId, formSchema, checkoutRules, shippingProfileRef</t>
+        </is>
+      </c>
+      <c r="F46" s="106" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G46" s="106" t="inlineStr">
+        <is>
+          <t>Sprint 2.8 - POS integration</t>
+        </is>
+      </c>
+      <c r="H46" s="106" t="inlineStr">
+        <is>
+          <t>☐</t>
         </is>
       </c>
     </row>
@@ -5053,7 +5238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="25" customWidth="1" style="106" min="1" max="1"/>
@@ -6645,7 +6830,7 @@
       </c>
       <c r="D31" s="140" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>EXISTS</t>
         </is>
       </c>
       <c r="E31" s="117" t="inlineStr">
@@ -6655,12 +6840,12 @@
       </c>
       <c r="F31" s="162" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>Sprint 2.7</t>
         </is>
       </c>
       <c r="G31" s="142" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="H31" s="172" t="inlineStr">
@@ -7144,6 +7329,224 @@
       <c r="J40" s="175" t="inlineStr">
         <is>
           <t>DONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="220" t="inlineStr">
+        <is>
+          <t>SPRINT 2.8 PLANNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="106" t="inlineStr">
+        <is>
+          <t>Activity Log (Redesign)</t>
+        </is>
+      </c>
+      <c r="B43" s="106" t="inlineStr">
+        <is>
+          <t>activity log viewer</t>
+        </is>
+      </c>
+      <c r="C43" s="106" t="inlineStr">
+        <is>
+          <t>/activity</t>
+        </is>
+      </c>
+      <c r="D43" s="106" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="E43" s="106" t="inlineStr">
+        <is>
+          <t>Full audit trail with filters, timeline, entity links, export — frontend-design skill</t>
+        </is>
+      </c>
+      <c r="F43" s="106" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G43" s="106" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="H43" s="106" t="inlineStr">
+        <is>
+          <t>DM - Dev</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="106" t="inlineStr">
+        <is>
+          <t>Settings Hub (Redesign)</t>
+        </is>
+      </c>
+      <c r="B44" s="106" t="inlineStr">
+        <is>
+          <t>settings/* (8+ tabs)</t>
+        </is>
+      </c>
+      <c r="C44" s="106" t="inlineStr">
+        <is>
+          <t>/settings/*</t>
+        </is>
+      </c>
+      <c r="D44" s="106" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="E44" s="106" t="inlineStr">
+        <is>
+          <t>Unified settings with auth providers, branding, API keys, team — frontend-design skill</t>
+        </is>
+      </c>
+      <c r="F44" s="106" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G44" s="106" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="H44" s="106" t="inlineStr">
+        <is>
+          <t>NK - Neha</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="106" t="inlineStr">
+        <is>
+          <t>Platform Admin Panel</t>
+        </is>
+      </c>
+      <c r="B45" s="106" t="inlineStr">
+        <is>
+          <t>— (new)</t>
+        </is>
+      </c>
+      <c r="C45" s="106" t="inlineStr">
+        <is>
+          <t>/admin/*</t>
+        </is>
+      </c>
+      <c r="D45" s="106" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="E45" s="106" t="inlineStr">
+        <is>
+          <t>User management, customer management, store oversight, metrics, platform config</t>
+        </is>
+      </c>
+      <c r="F45" s="106" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G45" s="106" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="H45" s="106" t="inlineStr">
+        <is>
+          <t>DM - Dev</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="106" t="inlineStr">
+        <is>
+          <t>Standard Delivery</t>
+        </is>
+      </c>
+      <c r="B46" s="106" t="inlineStr">
+        <is>
+          <t>standard-delivery/*</t>
+        </is>
+      </c>
+      <c r="C46" s="106" t="inlineStr">
+        <is>
+          <t>/delivery/standard</t>
+        </is>
+      </c>
+      <c r="D46" s="106" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="E46" s="106" t="inlineStr">
+        <is>
+          <t>Standard shipping workflow: orders, shipments, carrier assignment</t>
+        </is>
+      </c>
+      <c r="F46" s="106" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G46" s="106" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="H46" s="106" t="inlineStr">
+        <is>
+          <t>NK - Neha</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="106" t="inlineStr">
+        <is>
+          <t>Auth Provider Config</t>
+        </is>
+      </c>
+      <c r="B47" s="106" t="inlineStr">
+        <is>
+          <t>— (new)</t>
+        </is>
+      </c>
+      <c r="C47" s="106" t="inlineStr">
+        <is>
+          <t>/settings/auth-providers</t>
+        </is>
+      </c>
+      <c r="D47" s="106" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="E47" s="106" t="inlineStr">
+        <is>
+          <t>Auth0/Clerk/Cognito/Firebase provider setup, test connection, SAML/OIDC config</t>
+        </is>
+      </c>
+      <c r="F47" s="106" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G47" s="106" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="H47" s="106" t="inlineStr">
+        <is>
+          <t>NK - Neha</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="25" customWidth="1" style="106" min="1" max="1"/>
@@ -9839,6 +10242,266 @@
       <c r="J51" s="175" t="inlineStr">
         <is>
           <t>DONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="52"/>
+    <row r="53">
+      <c r="A53" s="220" t="inlineStr">
+        <is>
+          <t>SPRINT 2.8 PLANNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="106" t="inlineStr">
+        <is>
+          <t>Auth Provider Registry</t>
+        </is>
+      </c>
+      <c r="B54" s="106" t="inlineStr">
+        <is>
+          <t>— (new)</t>
+        </is>
+      </c>
+      <c r="C54" s="106" t="inlineStr">
+        <is>
+          <t>packages/core/src/auth/</t>
+        </is>
+      </c>
+      <c r="D54" s="106" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="E54" s="106" t="inlineStr">
+        <is>
+          <t>Multi-provider auth (Auth0, Clerk, Cognito, Firebase Auth, SAML, OIDC) with same BYOK pattern as routing/notifications</t>
+        </is>
+      </c>
+      <c r="F54" s="106" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G54" s="106" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="H54" s="106" t="inlineStr">
+        <is>
+          <t>AR - Arjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="106" t="inlineStr">
+        <is>
+          <t>Platform Admin API</t>
+        </is>
+      </c>
+      <c r="B55" s="106" t="inlineStr">
+        <is>
+          <t>— (new)</t>
+        </is>
+      </c>
+      <c r="C55" s="106" t="inlineStr">
+        <is>
+          <t>routes/admin.ts</t>
+        </is>
+      </c>
+      <c r="D55" s="106" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="E55" s="106" t="inlineStr">
+        <is>
+          <t>User CRUD, customer management, store oversight, platform metrics, config management</t>
+        </is>
+      </c>
+      <c r="F55" s="106" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G55" s="106" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="H55" s="106" t="inlineStr">
+        <is>
+          <t>PK - Priya</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="106" t="inlineStr">
+        <is>
+          <t>POS Integration</t>
+        </is>
+      </c>
+      <c r="B56" s="106" t="inlineStr">
+        <is>
+          <t>pos/posCustomFormService</t>
+        </is>
+      </c>
+      <c r="C56" s="106" t="inlineStr">
+        <is>
+          <t>routes/pos.ts + core/pos/</t>
+        </is>
+      </c>
+      <c r="D56" s="106" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="E56" s="106" t="inlineStr">
+        <is>
+          <t>POS checkout, custom form builder, POS-specific shipping profiles</t>
+        </is>
+      </c>
+      <c r="F56" s="106" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G56" s="106" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="H56" s="106" t="inlineStr">
+        <is>
+          <t>RG - Rohan</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="106" t="inlineStr">
+        <is>
+          <t>Docker Production Deploy</t>
+        </is>
+      </c>
+      <c r="B57" s="106" t="inlineStr">
+        <is>
+          <t>— (new)</t>
+        </is>
+      </c>
+      <c r="C57" s="106" t="inlineStr">
+        <is>
+          <t>infra/docker/</t>
+        </is>
+      </c>
+      <c r="D57" s="106" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="E57" s="106" t="inlineStr">
+        <is>
+          <t>Multi-stage Dockerfiles, docker-compose.prod.yml, health checks, env config</t>
+        </is>
+      </c>
+      <c r="F57" s="106" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G57" s="106" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="H57" s="106" t="inlineStr">
+        <is>
+          <t>AM - Aisha</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="106" t="inlineStr">
+        <is>
+          <t>API Hardening</t>
+        </is>
+      </c>
+      <c r="B58" s="106" t="inlineStr">
+        <is>
+          <t>— (existing)</t>
+        </is>
+      </c>
+      <c r="C58" s="106" t="inlineStr">
+        <is>
+          <t>routes/*.ts</t>
+        </is>
+      </c>
+      <c r="D58" s="106" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="E58" s="106" t="inlineStr">
+        <is>
+          <t>Zod validation on all routes, error standardization, OpenAPI spec generation</t>
+        </is>
+      </c>
+      <c r="F58" s="106" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G58" s="106" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="H58" s="106" t="inlineStr">
+        <is>
+          <t>PK - Priya</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="106" t="inlineStr">
+        <is>
+          <t>E2E Test Framework</t>
+        </is>
+      </c>
+      <c r="B59" s="106" t="inlineStr">
+        <is>
+          <t>— (new)</t>
+        </is>
+      </c>
+      <c r="C59" s="106" t="inlineStr">
+        <is>
+          <t>tests/e2e/</t>
+        </is>
+      </c>
+      <c r="D59" s="106" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="E59" s="106" t="inlineStr">
+        <is>
+          <t>Integration test suites, load testing scripts (k6), CI pipeline</t>
+        </is>
+      </c>
+      <c r="F59" s="106" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G59" s="106" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="H59" s="106" t="inlineStr">
+        <is>
+          <t>KS - Kavitha</t>
         </is>
       </c>
     </row>
@@ -9871,7 +10534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="106" min="1" max="1"/>
@@ -10215,7 +10878,7 @@
       </c>
       <c r="D7" s="117" t="inlineStr">
         <is>
-          <t>REDESIGNED</t>
+          <t>EXISTS</t>
         </is>
       </c>
       <c r="E7" s="117" t="inlineStr">
@@ -10225,12 +10888,12 @@
       </c>
       <c r="F7" s="146" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>Sprint 2.7 - process-manager with 4 workers</t>
         </is>
       </c>
       <c r="G7" s="142" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="H7" s="180" t="inlineStr">
@@ -11130,6 +11793,140 @@
       <c r="J24" s="175" t="inlineStr">
         <is>
           <t>DONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="220" t="inlineStr">
+        <is>
+          <t>SPRINT 2.8 PLANNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="106" t="inlineStr">
+        <is>
+          <t>Auth Provider Abstraction</t>
+        </is>
+      </c>
+      <c r="B27" s="106" t="inlineStr">
+        <is>
+          <t>— (new)</t>
+        </is>
+      </c>
+      <c r="C27" s="106" t="inlineStr">
+        <is>
+          <t>packages/core/src/auth/</t>
+        </is>
+      </c>
+      <c r="D27" s="106" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="E27" s="106" t="inlineStr">
+        <is>
+          <t>Multi-provider auth registry: Auth0, Clerk, AWS Cognito, Firebase Auth, generic OIDC, SAML 2.0 — same pattern as routing BYOK</t>
+        </is>
+      </c>
+      <c r="F27" s="106" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G27" s="106" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="H27" s="106" t="inlineStr">
+        <is>
+          <t>AR - Arjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="106" t="inlineStr">
+        <is>
+          <t>Docker Production Stack</t>
+        </is>
+      </c>
+      <c r="B28" s="106" t="inlineStr">
+        <is>
+          <t>Docker + Azure scripts</t>
+        </is>
+      </c>
+      <c r="C28" s="106" t="inlineStr">
+        <is>
+          <t>infra/docker/</t>
+        </is>
+      </c>
+      <c r="D28" s="106" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="E28" s="106" t="inlineStr">
+        <is>
+          <t>Multi-stage Dockerfiles, compose.prod.yml, Traefik reverse proxy, health checks, secrets management</t>
+        </is>
+      </c>
+      <c r="F28" s="106" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G28" s="106" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="H28" s="106" t="inlineStr">
+        <is>
+          <t>AM - Aisha</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="106" t="inlineStr">
+        <is>
+          <t>OpenAPI Spec</t>
+        </is>
+      </c>
+      <c r="B29" s="106" t="inlineStr">
+        <is>
+          <t>— (new)</t>
+        </is>
+      </c>
+      <c r="C29" s="106" t="inlineStr">
+        <is>
+          <t>docs/openapi.yaml</t>
+        </is>
+      </c>
+      <c r="D29" s="106" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="E29" s="106" t="inlineStr">
+        <is>
+          <t>Auto-generated OpenAPI 3.1 spec from Fastify schemas, Swagger UI at /docs</t>
+        </is>
+      </c>
+      <c r="F29" s="106" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G29" s="106" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="H29" s="106" t="inlineStr">
+        <is>
+          <t>PK - Priya</t>
         </is>
       </c>
     </row>
@@ -11162,7 +11959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="106" min="1" max="1"/>
@@ -13226,6 +14023,308 @@
       <c r="K36" s="144" t="inlineStr">
         <is>
           <t>DONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="220" t="inlineStr">
+        <is>
+          <t>SPRINT 2.8 PLANNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="106" t="inlineStr">
+        <is>
+          <t>Phase 7: Production</t>
+        </is>
+      </c>
+      <c r="B39" s="106" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="C39" s="106" t="inlineStr">
+        <is>
+          <t>Auth provider abstraction (Auth0, Clerk, Cognito, Firebase, OIDC, SAML)</t>
+        </is>
+      </c>
+      <c r="D39" s="106" t="inlineStr">
+        <is>
+          <t>Backend + Infra</t>
+        </is>
+      </c>
+      <c r="E39" s="106" t="inlineStr">
+        <is>
+          <t>2 weeks</t>
+        </is>
+      </c>
+      <c r="F39" s="106" t="inlineStr">
+        <is>
+          <t>Auth system</t>
+        </is>
+      </c>
+      <c r="G39" s="106" t="inlineStr">
+        <is>
+          <t>Multi-provider auth registry with BYOK pattern</t>
+        </is>
+      </c>
+      <c r="H39" s="106" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="106" t="inlineStr">
+        <is>
+          <t>Phase 7: Production</t>
+        </is>
+      </c>
+      <c r="B40" s="106" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="C40" s="106" t="inlineStr">
+        <is>
+          <t>Platform admin panel (user/customer management)</t>
+        </is>
+      </c>
+      <c r="D40" s="106" t="inlineStr">
+        <is>
+          <t>Backend + Frontend</t>
+        </is>
+      </c>
+      <c r="E40" s="106" t="inlineStr">
+        <is>
+          <t>2 weeks</t>
+        </is>
+      </c>
+      <c r="F40" s="106" t="inlineStr">
+        <is>
+          <t>Auth, RBAC</t>
+        </is>
+      </c>
+      <c r="G40" s="106" t="inlineStr">
+        <is>
+          <t>Admin dashboard for platform-level oversight</t>
+        </is>
+      </c>
+      <c r="H40" s="106" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="106" t="inlineStr">
+        <is>
+          <t>Phase 7: Production</t>
+        </is>
+      </c>
+      <c r="B41" s="106" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="C41" s="106" t="inlineStr">
+        <is>
+          <t>Activity log &amp; Settings redesign (frontend-design)</t>
+        </is>
+      </c>
+      <c r="D41" s="106" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E41" s="106" t="inlineStr">
+        <is>
+          <t>1 week</t>
+        </is>
+      </c>
+      <c r="F41" s="106" t="inlineStr">
+        <is>
+          <t>Audit, Settings</t>
+        </is>
+      </c>
+      <c r="G41" s="106" t="inlineStr">
+        <is>
+          <t>Production-grade UI with frontend-design skill</t>
+        </is>
+      </c>
+      <c r="H41" s="106" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="106" t="inlineStr">
+        <is>
+          <t>Phase 7: Production</t>
+        </is>
+      </c>
+      <c r="B42" s="106" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="C42" s="106" t="inlineStr">
+        <is>
+          <t>Docker production deployment</t>
+        </is>
+      </c>
+      <c r="D42" s="106" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="E42" s="106" t="inlineStr">
+        <is>
+          <t>1 week</t>
+        </is>
+      </c>
+      <c r="F42" s="106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="106" t="inlineStr">
+        <is>
+          <t>Multi-stage Dockerfiles, compose.prod.yml, health checks</t>
+        </is>
+      </c>
+      <c r="H42" s="106" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="106" t="inlineStr">
+        <is>
+          <t>Phase 7: Production</t>
+        </is>
+      </c>
+      <c r="B43" s="106" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="C43" s="106" t="inlineStr">
+        <is>
+          <t>POS integration</t>
+        </is>
+      </c>
+      <c r="D43" s="106" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E43" s="106" t="inlineStr">
+        <is>
+          <t>2 weeks</t>
+        </is>
+      </c>
+      <c r="F43" s="106" t="inlineStr">
+        <is>
+          <t>Products, Payments</t>
+        </is>
+      </c>
+      <c r="G43" s="106" t="inlineStr">
+        <is>
+          <t>POS checkout, custom forms</t>
+        </is>
+      </c>
+      <c r="H43" s="106" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="106" t="inlineStr">
+        <is>
+          <t>Phase 7: Production</t>
+        </is>
+      </c>
+      <c r="B44" s="106" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="C44" s="106" t="inlineStr">
+        <is>
+          <t>API hardening + OpenAPI spec</t>
+        </is>
+      </c>
+      <c r="D44" s="106" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E44" s="106" t="inlineStr">
+        <is>
+          <t>1 week</t>
+        </is>
+      </c>
+      <c r="F44" s="106" t="inlineStr">
+        <is>
+          <t>All routes</t>
+        </is>
+      </c>
+      <c r="G44" s="106" t="inlineStr">
+        <is>
+          <t>Zod validation, error standardization, Swagger UI</t>
+        </is>
+      </c>
+      <c r="H44" s="106" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="106" t="inlineStr">
+        <is>
+          <t>Phase 7: Production</t>
+        </is>
+      </c>
+      <c r="B45" s="106" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="C45" s="106" t="inlineStr">
+        <is>
+          <t>E2E tests + load testing</t>
+        </is>
+      </c>
+      <c r="D45" s="106" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="E45" s="106" t="inlineStr">
+        <is>
+          <t>1 week</t>
+        </is>
+      </c>
+      <c r="F45" s="106" t="inlineStr">
+        <is>
+          <t>All apps</t>
+        </is>
+      </c>
+      <c r="G45" s="106" t="inlineStr">
+        <is>
+          <t>Integration suites, k6 load tests, CI pipeline</t>
+        </is>
+      </c>
+      <c r="H45" s="106" t="inlineStr">
+        <is>
+          <t>☐</t>
         </is>
       </c>
     </row>
@@ -13272,6 +14371,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="107">
       <c r="A3" s="110" t="inlineStr">
         <is>
@@ -13910,6 +15010,7 @@
     <row r="34" ht="15" customHeight="1" s="107">
       <c r="F34" s="212" t="n"/>
     </row>
+    <row r="35"/>
     <row r="36" ht="15" customHeight="1" s="107">
       <c r="A36" s="106" t="inlineStr">
         <is>
@@ -13979,6 +15080,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="213" t="inlineStr">
         <is>
@@ -14038,20 +15140,20 @@
       <c r="F47" s="212" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="106" t="inlineStr">
         <is>
           <t>VS - Vikram</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="106" t="inlineStr">
         <is>
           <t>Saved views engine + widget manager core modules</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="C48" s="106" t="n">
         <v>6</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="106" t="n">
         <v>1566</v>
       </c>
       <c r="E48" s="217" t="inlineStr">
@@ -14061,20 +15163,20 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="106" t="inlineStr">
         <is>
           <t>PK - Priya</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="106" t="inlineStr">
         <is>
           <t>6 API routes (billing, support, features, views, widgets, collections)</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" s="106" t="n">
         <v>7</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="106" t="n">
         <v>2708</v>
       </c>
       <c r="E49" s="217" t="inlineStr">
@@ -14084,20 +15186,20 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="106" t="inlineStr">
         <is>
           <t>KS - Kavitha</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="106" t="inlineStr">
         <is>
           <t>7 test suites (subscription, quota, collections, support, views, widgets, process)</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="C50" s="106" t="n">
         <v>7</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="106" t="n">
         <v>3930</v>
       </c>
       <c r="E50" s="217" t="inlineStr">
@@ -14107,20 +15209,20 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="106" t="inlineStr">
         <is>
           <t>AM - Aisha</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="106" t="inlineStr">
         <is>
           <t>5 Shopify routes (billing, invoices, support, support detail, collections)</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" s="106" t="n">
         <v>5</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="106" t="n">
         <v>2233</v>
       </c>
       <c r="E51" s="217" t="inlineStr">
@@ -14129,6 +15231,8 @@
         </is>
       </c>
     </row>
+    <row r="52"/>
+    <row r="53"/>
     <row r="54">
       <c r="A54" s="213" t="inlineStr">
         <is>
@@ -14169,21 +15273,21 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="106" t="inlineStr">
         <is>
           <t>Data Models</t>
         </is>
       </c>
-      <c r="B56" t="n">
-        <v>39</v>
-      </c>
-      <c r="C56" t="n">
-        <v>28</v>
-      </c>
-      <c r="D56" t="n">
-        <v>2</v>
-      </c>
-      <c r="E56">
+      <c r="B56" s="106" t="n">
+        <v>43</v>
+      </c>
+      <c r="C56" s="106" t="n">
+        <v>37</v>
+      </c>
+      <c r="D56" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="106">
         <f>B56-C56-D56</f>
         <v/>
       </c>
@@ -14193,21 +15297,21 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="106" t="inlineStr">
         <is>
           <t>Feature Pages</t>
         </is>
       </c>
-      <c r="B57" t="n">
-        <v>34</v>
-      </c>
-      <c r="C57" t="n">
-        <v>31</v>
-      </c>
-      <c r="D57" t="n">
+      <c r="B57" s="106" t="n">
+        <v>39</v>
+      </c>
+      <c r="C57" s="106" t="n">
+        <v>32</v>
+      </c>
+      <c r="D57" s="106" t="n">
         <v>0</v>
       </c>
-      <c r="E57">
+      <c r="E57" s="106">
         <f>B57-C57-D57</f>
         <v/>
       </c>
@@ -14217,21 +15321,21 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="106" t="inlineStr">
         <is>
           <t>API Services</t>
         </is>
       </c>
-      <c r="B58" t="n">
+      <c r="B58" s="106" t="n">
+        <v>40</v>
+      </c>
+      <c r="C58" s="106" t="n">
         <v>34</v>
       </c>
-      <c r="C58" t="n">
-        <v>34</v>
-      </c>
-      <c r="D58" t="n">
+      <c r="D58" s="106" t="n">
         <v>0</v>
       </c>
-      <c r="E58">
+      <c r="E58" s="106">
         <f>B58-C58-D58</f>
         <v/>
       </c>
@@ -14241,21 +15345,21 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="106" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="B59" t="n">
-        <v>21</v>
-      </c>
-      <c r="C59" t="n">
-        <v>17</v>
-      </c>
-      <c r="D59" t="n">
+      <c r="B59" s="106" t="n">
+        <v>24</v>
+      </c>
+      <c r="C59" s="106" t="n">
+        <v>18</v>
+      </c>
+      <c r="D59" s="106" t="n">
         <v>0</v>
       </c>
-      <c r="E59">
+      <c r="E59" s="106">
         <f>B59-C59-D59</f>
         <v/>
       </c>
@@ -14265,21 +15369,21 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="106" t="inlineStr">
         <is>
           <t>Roadmap Items</t>
         </is>
       </c>
-      <c r="B60" t="n">
-        <v>35</v>
-      </c>
-      <c r="C60" t="n">
+      <c r="B60" s="106" t="n">
+        <v>42</v>
+      </c>
+      <c r="C60" s="106" t="n">
         <v>28</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="106" t="n">
         <v>2</v>
       </c>
-      <c r="E60">
+      <c r="E60" s="106">
         <f>B60-C60-D60</f>
         <v/>
       </c>
